--- a/equipos.xlsx
+++ b/equipos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\Documentos\Proyectos\random_team_selector\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Documents\GitHub\random_team_selector\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0017400F-BCD4-485B-BE7C-B3AF402AA8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85038D04-46E0-44F0-B712-408358D049B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1381,16 +1381,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D301"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1404,7 +1403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1416,7 +1415,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1428,7 +1427,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1440,7 +1439,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1452,7 +1451,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1464,7 +1463,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1476,7 +1475,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -1488,7 +1487,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1500,7 +1499,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -1512,7 +1511,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
@@ -1524,7 +1523,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
@@ -1536,7 +1535,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
@@ -1548,7 +1547,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
@@ -1560,7 +1559,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
@@ -1572,7 +1571,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
@@ -1584,7 +1583,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
@@ -1596,7 +1595,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
@@ -1608,7 +1607,7 @@
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
@@ -1620,7 +1619,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>4</v>
       </c>
@@ -1632,7 +1631,7 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>4</v>
       </c>
@@ -1644,7 +1643,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
@@ -1656,7 +1655,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
@@ -1680,7 +1679,7 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
@@ -1692,7 +1691,7 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -1704,7 +1703,7 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
@@ -1716,7 +1715,7 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
@@ -1728,7 +1727,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
@@ -1740,7 +1739,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>4</v>
       </c>
@@ -1752,7 +1751,7 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
@@ -1764,7 +1763,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>4</v>
       </c>
@@ -1776,7 +1775,7 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>4</v>
       </c>
@@ -1788,7 +1787,7 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>4</v>
       </c>
@@ -1800,7 +1799,7 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>4</v>
       </c>
@@ -1812,7 +1811,7 @@
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>4</v>
       </c>
@@ -1824,7 +1823,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
@@ -1836,7 +1835,7 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>4</v>
       </c>
@@ -1848,7 +1847,7 @@
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>4</v>
       </c>
@@ -1860,7 +1859,7 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>4</v>
       </c>
@@ -1872,7 +1871,7 @@
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>4</v>
       </c>
@@ -1884,7 +1883,7 @@
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>4</v>
       </c>
@@ -1896,7 +1895,7 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>4</v>
       </c>
@@ -1908,7 +1907,7 @@
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>4</v>
       </c>
@@ -1920,7 +1919,7 @@
       </c>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>4</v>
       </c>
@@ -1932,7 +1931,7 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>51</v>
       </c>
@@ -1944,7 +1943,7 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>51</v>
       </c>
@@ -1956,7 +1955,7 @@
       </c>
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
@@ -1968,7 +1967,7 @@
       </c>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>51</v>
       </c>
@@ -1980,7 +1979,7 @@
       </c>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>51</v>
       </c>
@@ -1994,7 +1993,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>51</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>51</v>
       </c>
@@ -2022,7 +2021,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>51</v>
       </c>
@@ -2034,7 +2033,7 @@
       </c>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>51</v>
       </c>
@@ -2046,7 +2045,7 @@
       </c>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>51</v>
       </c>
@@ -2058,7 +2057,7 @@
       </c>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>51</v>
       </c>
@@ -2070,7 +2069,7 @@
       </c>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>51</v>
       </c>
@@ -2082,7 +2081,7 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>51</v>
       </c>
@@ -2094,7 +2093,7 @@
       </c>
       <c r="D58" s="2"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>51</v>
       </c>
@@ -2108,7 +2107,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>51</v>
       </c>
@@ -2120,7 +2119,7 @@
       </c>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>51</v>
       </c>
@@ -2132,7 +2131,7 @@
       </c>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>51</v>
       </c>
@@ -2144,7 +2143,7 @@
       </c>
       <c r="D62" s="2"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>51</v>
       </c>
@@ -2156,7 +2155,7 @@
       </c>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>51</v>
       </c>
@@ -2168,7 +2167,7 @@
       </c>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>51</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>51</v>
       </c>
@@ -2194,7 +2193,7 @@
       </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>51</v>
       </c>
@@ -2206,7 +2205,7 @@
       </c>
       <c r="D67" s="2"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>51</v>
       </c>
@@ -2218,7 +2217,7 @@
       </c>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>51</v>
       </c>
@@ -2230,7 +2229,7 @@
       </c>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>51</v>
       </c>
@@ -2242,7 +2241,7 @@
       </c>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>51</v>
       </c>
@@ -2254,7 +2253,7 @@
       </c>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>51</v>
       </c>
@@ -2266,7 +2265,7 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>51</v>
       </c>
@@ -2278,7 +2277,7 @@
       </c>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>51</v>
       </c>
@@ -2290,7 +2289,7 @@
       </c>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>51</v>
       </c>
@@ -2302,7 +2301,7 @@
       </c>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>51</v>
       </c>
@@ -2314,7 +2313,7 @@
       </c>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>51</v>
       </c>
@@ -2326,7 +2325,7 @@
       </c>
       <c r="D77" s="2"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>51</v>
       </c>
@@ -2338,7 +2337,7 @@
       </c>
       <c r="D78" s="2"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>51</v>
       </c>
@@ -2350,7 +2349,7 @@
       </c>
       <c r="D79" s="2"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>51</v>
       </c>
@@ -2362,7 +2361,7 @@
       </c>
       <c r="D80" s="2"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>51</v>
       </c>
@@ -2374,7 +2373,7 @@
       </c>
       <c r="D81" s="2"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>51</v>
       </c>
@@ -2386,7 +2385,7 @@
       </c>
       <c r="D82" s="2"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>51</v>
       </c>
@@ -2398,7 +2397,7 @@
       </c>
       <c r="D83" s="2"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>51</v>
       </c>
@@ -2410,7 +2409,7 @@
       </c>
       <c r="D84" s="2"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>51</v>
       </c>
@@ -2422,7 +2421,7 @@
       </c>
       <c r="D85" s="2"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>51</v>
       </c>
@@ -2434,7 +2433,7 @@
       </c>
       <c r="D86" s="2"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>51</v>
       </c>
@@ -2446,7 +2445,7 @@
       </c>
       <c r="D87" s="2"/>
     </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>96</v>
       </c>
@@ -2458,7 +2457,7 @@
       </c>
       <c r="D88" s="2"/>
     </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>96</v>
       </c>
@@ -2470,7 +2469,7 @@
       </c>
       <c r="D89" s="2"/>
     </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>96</v>
       </c>
@@ -2482,7 +2481,7 @@
       </c>
       <c r="D90" s="2"/>
     </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>96</v>
       </c>
@@ -2494,7 +2493,7 @@
       </c>
       <c r="D91" s="2"/>
     </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>96</v>
       </c>
@@ -2506,7 +2505,7 @@
       </c>
       <c r="D92" s="2"/>
     </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>96</v>
       </c>
@@ -2518,7 +2517,7 @@
       </c>
       <c r="D93" s="2"/>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>96</v>
       </c>
@@ -2530,7 +2529,7 @@
       </c>
       <c r="D94" s="2"/>
     </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>96</v>
       </c>
@@ -2542,7 +2541,7 @@
       </c>
       <c r="D95" s="2"/>
     </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>96</v>
       </c>
@@ -2554,7 +2553,7 @@
       </c>
       <c r="D96" s="2"/>
     </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>96</v>
       </c>
@@ -2566,7 +2565,7 @@
       </c>
       <c r="D97" s="2"/>
     </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>96</v>
       </c>
@@ -2578,7 +2577,7 @@
       </c>
       <c r="D98" s="2"/>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>96</v>
       </c>
@@ -2590,7 +2589,7 @@
       </c>
       <c r="D99" s="2"/>
     </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>96</v>
       </c>
@@ -2602,7 +2601,7 @@
       </c>
       <c r="D100" s="2"/>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>96</v>
       </c>
@@ -2614,7 +2613,7 @@
       </c>
       <c r="D101" s="2"/>
     </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>96</v>
       </c>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="D102" s="2"/>
     </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>96</v>
       </c>
@@ -2638,7 +2637,7 @@
       </c>
       <c r="D103" s="2"/>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>96</v>
       </c>
@@ -2650,7 +2649,7 @@
       </c>
       <c r="D104" s="2"/>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>96</v>
       </c>
@@ -2662,7 +2661,7 @@
       </c>
       <c r="D105" s="2"/>
     </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>96</v>
       </c>
@@ -2674,7 +2673,7 @@
       </c>
       <c r="D106" s="2"/>
     </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>96</v>
       </c>
@@ -2686,7 +2685,7 @@
       </c>
       <c r="D107" s="2"/>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>96</v>
       </c>
@@ -2698,7 +2697,7 @@
       </c>
       <c r="D108" s="2"/>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>96</v>
       </c>
@@ -2710,7 +2709,7 @@
       </c>
       <c r="D109" s="2"/>
     </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>96</v>
       </c>
@@ -2722,7 +2721,7 @@
       </c>
       <c r="D110" s="2"/>
     </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>96</v>
       </c>
@@ -2734,7 +2733,7 @@
       </c>
       <c r="D111" s="2"/>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>96</v>
       </c>
@@ -2746,7 +2745,7 @@
       </c>
       <c r="D112" s="2"/>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>96</v>
       </c>
@@ -2758,7 +2757,7 @@
       </c>
       <c r="D113" s="2"/>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>96</v>
       </c>
@@ -2770,7 +2769,7 @@
       </c>
       <c r="D114" s="2"/>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>96</v>
       </c>
@@ -2782,7 +2781,7 @@
       </c>
       <c r="D115" s="2"/>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>96</v>
       </c>
@@ -2794,7 +2793,7 @@
       </c>
       <c r="D116" s="2"/>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>96</v>
       </c>
@@ -2806,7 +2805,7 @@
       </c>
       <c r="D117" s="2"/>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>96</v>
       </c>
@@ -2818,7 +2817,7 @@
       </c>
       <c r="D118" s="2"/>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>96</v>
       </c>
@@ -2830,7 +2829,7 @@
       </c>
       <c r="D119" s="2"/>
     </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>96</v>
       </c>
@@ -2842,7 +2841,7 @@
       </c>
       <c r="D120" s="2"/>
     </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>96</v>
       </c>
@@ -2854,7 +2853,7 @@
       </c>
       <c r="D121" s="2"/>
     </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>96</v>
       </c>
@@ -2866,7 +2865,7 @@
       </c>
       <c r="D122" s="2"/>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>96</v>
       </c>
@@ -2878,7 +2877,7 @@
       </c>
       <c r="D123" s="2"/>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>96</v>
       </c>
@@ -2890,7 +2889,7 @@
       </c>
       <c r="D124" s="2"/>
     </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>96</v>
       </c>
@@ -2902,7 +2901,7 @@
       </c>
       <c r="D125" s="2"/>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>96</v>
       </c>
@@ -2914,7 +2913,7 @@
       </c>
       <c r="D126" s="2"/>
     </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>96</v>
       </c>
@@ -2926,7 +2925,7 @@
       </c>
       <c r="D127" s="2"/>
     </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>139</v>
       </c>
@@ -2938,7 +2937,7 @@
       </c>
       <c r="D128" s="2"/>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>139</v>
       </c>
@@ -2950,7 +2949,7 @@
       </c>
       <c r="D129" s="2"/>
     </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>139</v>
       </c>
@@ -2962,7 +2961,7 @@
       </c>
       <c r="D130" s="2"/>
     </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>139</v>
       </c>
@@ -2974,7 +2973,7 @@
       </c>
       <c r="D131" s="2"/>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>139</v>
       </c>
@@ -2986,7 +2985,7 @@
       </c>
       <c r="D132" s="2"/>
     </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>139</v>
       </c>
@@ -2998,7 +2997,7 @@
       </c>
       <c r="D133" s="2"/>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>139</v>
       </c>
@@ -3010,7 +3009,7 @@
       </c>
       <c r="D134" s="2"/>
     </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>139</v>
       </c>
@@ -3022,7 +3021,7 @@
       </c>
       <c r="D135" s="2"/>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>139</v>
       </c>
@@ -3034,7 +3033,7 @@
       </c>
       <c r="D136" s="2"/>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>139</v>
       </c>
@@ -3046,7 +3045,7 @@
       </c>
       <c r="D137" s="2"/>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>139</v>
       </c>
@@ -3058,7 +3057,7 @@
       </c>
       <c r="D138" s="2"/>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>139</v>
       </c>
@@ -3070,7 +3069,7 @@
       </c>
       <c r="D139" s="2"/>
     </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>139</v>
       </c>
@@ -3082,7 +3081,7 @@
       </c>
       <c r="D140" s="2"/>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>139</v>
       </c>
@@ -3094,7 +3093,7 @@
       </c>
       <c r="D141" s="2"/>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>139</v>
       </c>
@@ -3106,7 +3105,7 @@
       </c>
       <c r="D142" s="2"/>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>139</v>
       </c>
@@ -3118,7 +3117,7 @@
       </c>
       <c r="D143" s="2"/>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>139</v>
       </c>
@@ -3130,7 +3129,7 @@
       </c>
       <c r="D144" s="2"/>
     </row>
-    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>139</v>
       </c>
@@ -3142,7 +3141,7 @@
       </c>
       <c r="D145" s="2"/>
     </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>139</v>
       </c>
@@ -3154,7 +3153,7 @@
       </c>
       <c r="D146" s="2"/>
     </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>139</v>
       </c>
@@ -3166,7 +3165,7 @@
       </c>
       <c r="D147" s="2"/>
     </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>139</v>
       </c>
@@ -3178,7 +3177,7 @@
       </c>
       <c r="D148" s="2"/>
     </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>139</v>
       </c>
@@ -3190,7 +3189,7 @@
       </c>
       <c r="D149" s="2"/>
     </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>139</v>
       </c>
@@ -3202,7 +3201,7 @@
       </c>
       <c r="D150" s="2"/>
     </row>
-    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>139</v>
       </c>
@@ -3214,7 +3213,7 @@
       </c>
       <c r="D151" s="2"/>
     </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>139</v>
       </c>
@@ -3226,7 +3225,7 @@
       </c>
       <c r="D152" s="2"/>
     </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>139</v>
       </c>
@@ -3238,7 +3237,7 @@
       </c>
       <c r="D153" s="2"/>
     </row>
-    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>139</v>
       </c>
@@ -3250,7 +3249,7 @@
       </c>
       <c r="D154" s="2"/>
     </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>139</v>
       </c>
@@ -3262,7 +3261,7 @@
       </c>
       <c r="D155" s="2"/>
     </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>139</v>
       </c>
@@ -3274,7 +3273,7 @@
       </c>
       <c r="D156" s="2"/>
     </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>139</v>
       </c>
@@ -3286,7 +3285,7 @@
       </c>
       <c r="D157" s="2"/>
     </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>139</v>
       </c>
@@ -3298,7 +3297,7 @@
       </c>
       <c r="D158" s="2"/>
     </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>139</v>
       </c>
@@ -3310,7 +3309,7 @@
       </c>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>139</v>
       </c>
@@ -3322,7 +3321,7 @@
       </c>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>139</v>
       </c>
@@ -3334,7 +3333,7 @@
       </c>
       <c r="D161" s="2"/>
     </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>139</v>
       </c>
@@ -3346,7 +3345,7 @@
       </c>
       <c r="D162" s="2"/>
     </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>177</v>
       </c>
@@ -3358,7 +3357,7 @@
       </c>
       <c r="D163" s="2"/>
     </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>177</v>
       </c>
@@ -3370,7 +3369,7 @@
       </c>
       <c r="D164" s="2"/>
     </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>177</v>
       </c>
@@ -3382,7 +3381,7 @@
       </c>
       <c r="D165" s="2"/>
     </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>177</v>
       </c>
@@ -3394,7 +3393,7 @@
       </c>
       <c r="D166" s="2"/>
     </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>177</v>
       </c>
@@ -3406,7 +3405,7 @@
       </c>
       <c r="D167" s="2"/>
     </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>177</v>
       </c>
@@ -3418,7 +3417,7 @@
       </c>
       <c r="D168" s="2"/>
     </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>177</v>
       </c>
@@ -3430,7 +3429,7 @@
       </c>
       <c r="D169" s="2"/>
     </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>177</v>
       </c>
@@ -3442,7 +3441,7 @@
       </c>
       <c r="D170" s="2"/>
     </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>177</v>
       </c>
@@ -3454,7 +3453,7 @@
       </c>
       <c r="D171" s="2"/>
     </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>177</v>
       </c>
@@ -3466,7 +3465,7 @@
       </c>
       <c r="D172" s="2"/>
     </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>177</v>
       </c>
@@ -3478,7 +3477,7 @@
       </c>
       <c r="D173" s="2"/>
     </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>177</v>
       </c>
@@ -3490,7 +3489,7 @@
       </c>
       <c r="D174" s="2"/>
     </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>177</v>
       </c>
@@ -3502,7 +3501,7 @@
       </c>
       <c r="D175" s="2"/>
     </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>177</v>
       </c>
@@ -3514,7 +3513,7 @@
       </c>
       <c r="D176" s="2"/>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>177</v>
       </c>
@@ -3526,7 +3525,7 @@
       </c>
       <c r="D177" s="2"/>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>177</v>
       </c>
@@ -3538,7 +3537,7 @@
       </c>
       <c r="D178" s="2"/>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>177</v>
       </c>
@@ -3550,7 +3549,7 @@
       </c>
       <c r="D179" s="2"/>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>177</v>
       </c>
@@ -3562,7 +3561,7 @@
       </c>
       <c r="D180" s="2"/>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>177</v>
       </c>
@@ -3574,7 +3573,7 @@
       </c>
       <c r="D181" s="2"/>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>177</v>
       </c>
@@ -3586,7 +3585,7 @@
       </c>
       <c r="D182" s="2"/>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>177</v>
       </c>
@@ -3598,7 +3597,7 @@
       </c>
       <c r="D183" s="2"/>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>177</v>
       </c>
@@ -3610,7 +3609,7 @@
       </c>
       <c r="D184" s="2"/>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>177</v>
       </c>
@@ -3622,7 +3621,7 @@
       </c>
       <c r="D185" s="2"/>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>177</v>
       </c>
@@ -3634,7 +3633,7 @@
       </c>
       <c r="D186" s="2"/>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>177</v>
       </c>
@@ -3646,7 +3645,7 @@
       </c>
       <c r="D187" s="2"/>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>177</v>
       </c>
@@ -3658,7 +3657,7 @@
       </c>
       <c r="D188" s="2"/>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>177</v>
       </c>
@@ -3670,7 +3669,7 @@
       </c>
       <c r="D189" s="2"/>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>177</v>
       </c>
@@ -3682,7 +3681,7 @@
       </c>
       <c r="D190" s="2"/>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>177</v>
       </c>
@@ -3694,7 +3693,7 @@
       </c>
       <c r="D191" s="2"/>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>177</v>
       </c>
@@ -3706,7 +3705,7 @@
       </c>
       <c r="D192" s="2"/>
     </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>177</v>
       </c>
@@ -3718,7 +3717,7 @@
       </c>
       <c r="D193" s="2"/>
     </row>
-    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>177</v>
       </c>
@@ -3730,7 +3729,7 @@
       </c>
       <c r="D194" s="2"/>
     </row>
-    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>177</v>
       </c>
@@ -3742,7 +3741,7 @@
       </c>
       <c r="D195" s="2"/>
     </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>177</v>
       </c>
@@ -3754,7 +3753,7 @@
       </c>
       <c r="D196" s="2"/>
     </row>
-    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>177</v>
       </c>
@@ -3766,7 +3765,7 @@
       </c>
       <c r="D197" s="2"/>
     </row>
-    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>177</v>
       </c>
@@ -3778,7 +3777,7 @@
       </c>
       <c r="D198" s="2"/>
     </row>
-    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>216</v>
       </c>
@@ -3790,7 +3789,7 @@
       </c>
       <c r="D199" s="2"/>
     </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>216</v>
       </c>
@@ -3802,7 +3801,7 @@
       </c>
       <c r="D200" s="2"/>
     </row>
-    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>216</v>
       </c>
@@ -3814,7 +3813,7 @@
       </c>
       <c r="D201" s="2"/>
     </row>
-    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>216</v>
       </c>
@@ -3826,7 +3825,7 @@
       </c>
       <c r="D202" s="2"/>
     </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>216</v>
       </c>
@@ -3838,7 +3837,7 @@
       </c>
       <c r="D203" s="2"/>
     </row>
-    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>216</v>
       </c>
@@ -3850,7 +3849,7 @@
       </c>
       <c r="D204" s="2"/>
     </row>
-    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>216</v>
       </c>
@@ -3862,7 +3861,7 @@
       </c>
       <c r="D205" s="2"/>
     </row>
-    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>216</v>
       </c>
@@ -3874,7 +3873,7 @@
       </c>
       <c r="D206" s="2"/>
     </row>
-    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>216</v>
       </c>
@@ -3886,7 +3885,7 @@
       </c>
       <c r="D207" s="2"/>
     </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>216</v>
       </c>
@@ -3898,7 +3897,7 @@
       </c>
       <c r="D208" s="2"/>
     </row>
-    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>216</v>
       </c>
@@ -3910,7 +3909,7 @@
       </c>
       <c r="D209" s="2"/>
     </row>
-    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>216</v>
       </c>
@@ -3922,7 +3921,7 @@
       </c>
       <c r="D210" s="2"/>
     </row>
-    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>216</v>
       </c>
@@ -3934,7 +3933,7 @@
       </c>
       <c r="D211" s="2"/>
     </row>
-    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>216</v>
       </c>
@@ -3946,7 +3945,7 @@
       </c>
       <c r="D212" s="2"/>
     </row>
-    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>216</v>
       </c>
@@ -3958,7 +3957,7 @@
       </c>
       <c r="D213" s="2"/>
     </row>
-    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>216</v>
       </c>
@@ -3970,7 +3969,7 @@
       </c>
       <c r="D214" s="2"/>
     </row>
-    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>216</v>
       </c>
@@ -3982,7 +3981,7 @@
       </c>
       <c r="D215" s="2"/>
     </row>
-    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>216</v>
       </c>
@@ -3994,7 +3993,7 @@
       </c>
       <c r="D216" s="2"/>
     </row>
-    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>236</v>
       </c>
@@ -4006,7 +4005,7 @@
       </c>
       <c r="D217" s="2"/>
     </row>
-    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>236</v>
       </c>
@@ -4018,7 +4017,7 @@
       </c>
       <c r="D218" s="2"/>
     </row>
-    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>236</v>
       </c>
@@ -4030,7 +4029,7 @@
       </c>
       <c r="D219" s="2"/>
     </row>
-    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>236</v>
       </c>
@@ -4042,7 +4041,7 @@
       </c>
       <c r="D220" s="2"/>
     </row>
-    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>236</v>
       </c>
@@ -4054,7 +4053,7 @@
       </c>
       <c r="D221" s="2"/>
     </row>
-    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>236</v>
       </c>
@@ -4066,7 +4065,7 @@
       </c>
       <c r="D222" s="2"/>
     </row>
-    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>236</v>
       </c>
@@ -4078,7 +4077,7 @@
       </c>
       <c r="D223" s="2"/>
     </row>
-    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>236</v>
       </c>
@@ -4090,7 +4089,7 @@
       </c>
       <c r="D224" s="2"/>
     </row>
-    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>236</v>
       </c>
@@ -4102,7 +4101,7 @@
       </c>
       <c r="D225" s="2"/>
     </row>
-    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>236</v>
       </c>
@@ -4114,7 +4113,7 @@
       </c>
       <c r="D226" s="2"/>
     </row>
-    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>236</v>
       </c>
@@ -4126,7 +4125,7 @@
       </c>
       <c r="D227" s="2"/>
     </row>
-    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>236</v>
       </c>
@@ -4138,7 +4137,7 @@
       </c>
       <c r="D228" s="2"/>
     </row>
-    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>236</v>
       </c>
@@ -4150,7 +4149,7 @@
       </c>
       <c r="D229" s="2"/>
     </row>
-    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>236</v>
       </c>
@@ -4162,7 +4161,7 @@
       </c>
       <c r="D230" s="2"/>
     </row>
-    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>236</v>
       </c>
@@ -4174,7 +4173,7 @@
       </c>
       <c r="D231" s="2"/>
     </row>
-    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>236</v>
       </c>
@@ -4186,7 +4185,7 @@
       </c>
       <c r="D232" s="2"/>
     </row>
-    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>236</v>
       </c>
@@ -4198,7 +4197,7 @@
       </c>
       <c r="D233" s="2"/>
     </row>
-    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>236</v>
       </c>
@@ -4210,7 +4209,7 @@
       </c>
       <c r="D234" s="2"/>
     </row>
-    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>256</v>
       </c>
@@ -4222,7 +4221,7 @@
       </c>
       <c r="D235" s="2"/>
     </row>
-    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>256</v>
       </c>
@@ -4234,7 +4233,7 @@
       </c>
       <c r="D236" s="2"/>
     </row>
-    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>256</v>
       </c>
@@ -4246,7 +4245,7 @@
       </c>
       <c r="D237" s="2"/>
     </row>
-    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>256</v>
       </c>
@@ -4258,7 +4257,7 @@
       </c>
       <c r="D238" s="2"/>
     </row>
-    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>256</v>
       </c>
@@ -4270,7 +4269,7 @@
       </c>
       <c r="D239" s="2"/>
     </row>
-    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>256</v>
       </c>
@@ -4282,7 +4281,7 @@
       </c>
       <c r="D240" s="2"/>
     </row>
-    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>256</v>
       </c>
@@ -4294,7 +4293,7 @@
       </c>
       <c r="D241" s="2"/>
     </row>
-    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>256</v>
       </c>
@@ -4306,7 +4305,7 @@
       </c>
       <c r="D242" s="2"/>
     </row>
-    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>256</v>
       </c>
@@ -4318,7 +4317,7 @@
       </c>
       <c r="D243" s="2"/>
     </row>
-    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>256</v>
       </c>
@@ -4330,7 +4329,7 @@
       </c>
       <c r="D244" s="2"/>
     </row>
-    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>256</v>
       </c>
@@ -4342,7 +4341,7 @@
       </c>
       <c r="D245" s="2"/>
     </row>
-    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>256</v>
       </c>
@@ -4354,7 +4353,7 @@
       </c>
       <c r="D246" s="2"/>
     </row>
-    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>256</v>
       </c>
@@ -4366,7 +4365,7 @@
       </c>
       <c r="D247" s="2"/>
     </row>
-    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>256</v>
       </c>
@@ -4378,7 +4377,7 @@
       </c>
       <c r="D248" s="2"/>
     </row>
-    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>256</v>
       </c>
@@ -4390,7 +4389,7 @@
       </c>
       <c r="D249" s="2"/>
     </row>
-    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>256</v>
       </c>
@@ -4402,7 +4401,7 @@
       </c>
       <c r="D250" s="2"/>
     </row>
-    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>256</v>
       </c>
@@ -4414,7 +4413,7 @@
       </c>
       <c r="D251" s="2"/>
     </row>
-    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>256</v>
       </c>
@@ -4426,7 +4425,7 @@
       </c>
       <c r="D252" s="2"/>
     </row>
-    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>256</v>
       </c>
@@ -4438,7 +4437,7 @@
       </c>
       <c r="D253" s="2"/>
     </row>
-    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>277</v>
       </c>
@@ -4450,7 +4449,7 @@
       </c>
       <c r="D254" s="2"/>
     </row>
-    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>277</v>
       </c>
@@ -4462,7 +4461,7 @@
       </c>
       <c r="D255" s="2"/>
     </row>
-    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>277</v>
       </c>
@@ -4474,7 +4473,7 @@
       </c>
       <c r="D256" s="2"/>
     </row>
-    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>277</v>
       </c>
@@ -4486,7 +4485,7 @@
       </c>
       <c r="D257" s="2"/>
     </row>
-    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>277</v>
       </c>
@@ -4498,7 +4497,7 @@
       </c>
       <c r="D258" s="2"/>
     </row>
-    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>277</v>
       </c>
@@ -4510,7 +4509,7 @@
       </c>
       <c r="D259" s="2"/>
     </row>
-    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>277</v>
       </c>
@@ -4522,7 +4521,7 @@
       </c>
       <c r="D260" s="2"/>
     </row>
-    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>277</v>
       </c>
@@ -4534,7 +4533,7 @@
       </c>
       <c r="D261" s="2"/>
     </row>
-    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>277</v>
       </c>
@@ -4546,7 +4545,7 @@
       </c>
       <c r="D262" s="2"/>
     </row>
-    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>277</v>
       </c>
@@ -4558,7 +4557,7 @@
       </c>
       <c r="D263" s="2"/>
     </row>
-    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>277</v>
       </c>
@@ -4570,7 +4569,7 @@
       </c>
       <c r="D264" s="2"/>
     </row>
-    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>277</v>
       </c>
@@ -4582,7 +4581,7 @@
       </c>
       <c r="D265" s="2"/>
     </row>
-    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>277</v>
       </c>
@@ -4594,7 +4593,7 @@
       </c>
       <c r="D266" s="2"/>
     </row>
-    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>277</v>
       </c>
@@ -4606,7 +4605,7 @@
       </c>
       <c r="D267" s="2"/>
     </row>
-    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>277</v>
       </c>
@@ -4618,7 +4617,7 @@
       </c>
       <c r="D268" s="2"/>
     </row>
-    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>277</v>
       </c>
@@ -4630,7 +4629,7 @@
       </c>
       <c r="D269" s="2"/>
     </row>
-    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>277</v>
       </c>
@@ -4642,7 +4641,7 @@
       </c>
       <c r="D270" s="2"/>
     </row>
-    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>277</v>
       </c>
@@ -4654,7 +4653,7 @@
       </c>
       <c r="D271" s="2"/>
     </row>
-    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>277</v>
       </c>
@@ -4666,7 +4665,7 @@
       </c>
       <c r="D272" s="2"/>
     </row>
-    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>277</v>
       </c>
@@ -4678,7 +4677,7 @@
       </c>
       <c r="D273" s="2"/>
     </row>
-    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>299</v>
       </c>
@@ -4690,7 +4689,7 @@
       </c>
       <c r="D274" s="2"/>
     </row>
-    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>299</v>
       </c>
@@ -4702,7 +4701,7 @@
       </c>
       <c r="D275" s="2"/>
     </row>
-    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>299</v>
       </c>
@@ -4714,7 +4713,7 @@
       </c>
       <c r="D276" s="2"/>
     </row>
-    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>299</v>
       </c>
@@ -4726,7 +4725,7 @@
       </c>
       <c r="D277" s="2"/>
     </row>
-    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>299</v>
       </c>
@@ -4738,7 +4737,7 @@
       </c>
       <c r="D278" s="2"/>
     </row>
-    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>299</v>
       </c>
@@ -4750,7 +4749,7 @@
       </c>
       <c r="D279" s="2"/>
     </row>
-    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>299</v>
       </c>
@@ -4762,7 +4761,7 @@
       </c>
       <c r="D280" s="2"/>
     </row>
-    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>299</v>
       </c>
@@ -4774,7 +4773,7 @@
       </c>
       <c r="D281" s="2"/>
     </row>
-    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>299</v>
       </c>
@@ -4786,7 +4785,7 @@
       </c>
       <c r="D282" s="2"/>
     </row>
-    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>299</v>
       </c>
@@ -4798,7 +4797,7 @@
       </c>
       <c r="D283" s="2"/>
     </row>
-    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>299</v>
       </c>
@@ -4810,7 +4809,7 @@
       </c>
       <c r="D284" s="2"/>
     </row>
-    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>299</v>
       </c>
@@ -4822,7 +4821,7 @@
       </c>
       <c r="D285" s="2"/>
     </row>
-    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>299</v>
       </c>
@@ -4834,7 +4833,7 @@
       </c>
       <c r="D286" s="2"/>
     </row>
-    <row r="287" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>299</v>
       </c>
@@ -4846,7 +4845,7 @@
       </c>
       <c r="D287" s="2"/>
     </row>
-    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>299</v>
       </c>
@@ -4858,7 +4857,7 @@
       </c>
       <c r="D288" s="2"/>
     </row>
-    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>299</v>
       </c>
@@ -4870,7 +4869,7 @@
       </c>
       <c r="D289" s="2"/>
     </row>
-    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>299</v>
       </c>
@@ -4882,7 +4881,7 @@
       </c>
       <c r="D290" s="2"/>
     </row>
-    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>299</v>
       </c>
@@ -4894,7 +4893,7 @@
       </c>
       <c r="D291" s="2"/>
     </row>
-    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>299</v>
       </c>
@@ -4906,7 +4905,7 @@
       </c>
       <c r="D292" s="2"/>
     </row>
-    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>299</v>
       </c>
@@ -4918,7 +4917,7 @@
       </c>
       <c r="D293" s="2"/>
     </row>
-    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>299</v>
       </c>
@@ -4930,7 +4929,7 @@
       </c>
       <c r="D294" s="2"/>
     </row>
-    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>299</v>
       </c>
@@ -4942,7 +4941,7 @@
       </c>
       <c r="D295" s="2"/>
     </row>
-    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>299</v>
       </c>
@@ -4954,7 +4953,7 @@
       </c>
       <c r="D296" s="2"/>
     </row>
-    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>299</v>
       </c>
@@ -4966,7 +4965,7 @@
       </c>
       <c r="D297" s="2"/>
     </row>
-    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>299</v>
       </c>
@@ -4978,7 +4977,7 @@
       </c>
       <c r="D298" s="2"/>
     </row>
-    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>299</v>
       </c>
@@ -4990,7 +4989,7 @@
       </c>
       <c r="D299" s="2"/>
     </row>
-    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>299</v>
       </c>
@@ -5002,7 +5001,7 @@
       </c>
       <c r="D300" s="2"/>
     </row>
-    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>299</v>
       </c>
@@ -5015,13 +5014,7 @@
       <c r="D301" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D301" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="España"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D301" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>